--- a/scripts/EU_Figures/OPH_Figures.xlsx
+++ b/scripts/EU_Figures/OPH_Figures.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjusted Eurozone GVAH" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unadjusted Eurozone GVAH" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjusted Eurozone GVA per hour" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unadjusted Eurozone GVA per hour" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2835197.45</v>
+        <v>2835194.5</v>
       </c>
       <c r="C2" t="n">
         <v>65709428</v>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2837563.4</v>
+        <v>2837565.36</v>
       </c>
       <c r="C3" t="n">
         <v>65729377</v>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2843341.31</v>
+        <v>2843343.26</v>
       </c>
       <c r="C4" t="n">
         <v>66026966</v>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2860133.55</v>
+        <v>2860130.59</v>
       </c>
       <c r="C5" t="n">
         <v>66070125</v>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2861700.59</v>
+        <v>2861692.71</v>
       </c>
       <c r="C6" t="n">
         <v>66354796</v>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2869551.73</v>
+        <v>2869555.31</v>
       </c>
       <c r="C7" t="n">
         <v>66445746</v>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2873979.6</v>
+        <v>2873989.72</v>
       </c>
       <c r="C8" t="n">
         <v>66405191</v>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2876843.71</v>
+        <v>2876839.09</v>
       </c>
       <c r="C9" t="n">
         <v>66755243</v>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2887655.39</v>
+        <v>2887639.31</v>
       </c>
       <c r="C10" t="n">
         <v>66707656</v>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2893118.9</v>
+        <v>2893123.3</v>
       </c>
       <c r="C11" t="n">
         <v>66648222</v>
@@ -668,7 +668,7 @@
         <v>0.28</v>
       </c>
       <c r="F11" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="12">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2902323.15</v>
+        <v>2902342.28</v>
       </c>
       <c r="C12" t="n">
         <v>66857011</v>
@@ -687,7 +687,7 @@
         <v>43.41</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F12" t="n">
         <v>0.3</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2912662.79</v>
+        <v>2912653.26</v>
       </c>
       <c r="C13" t="n">
         <v>67234318</v>
